--- a/data/final/output/Criterion_level_performance_2030_2040.xlsx
+++ b/data/final/output/Criterion_level_performance_2030_2040.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,49 +504,49 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Carbon removal for fossil electricity generation plants</t>
+          <t>Minimum tariffs for photovoltaic systems &lt;= 150 Kw</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.012 (8)</t>
+          <t>0.033 (21)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.094 (13)</t>
+          <t>0.226 (48)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.000 (1)</t>
+          <t>0.220 (43)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.102 (35)</t>
+          <t>0.136 (28)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.041 (1)</t>
+          <t>0.204 (34)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.201 (1)</t>
+          <t>0.151 (12)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.839 (1)</t>
+          <t>0.542 (43)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P+D subsidy on DACCS</t>
+          <t>Carbon removal for fossil electricity generation plants</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -566,39 +566,39 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.170 (1)</t>
+          <t>0.102 (35)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.122 (10)</t>
+          <t>0.041 (1)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.100 (29)</t>
+          <t>0.201 (1)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.801 (7)</t>
+          <t>0.839 (1)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Project planning grants for Alpine PV</t>
+          <t>P+D subsidy on DACCS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.024 (16)</t>
+          <t>0.012 (8)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.140 (20)</t>
+          <t>0.094 (13)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -613,44 +613,44 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.041 (1)</t>
+          <t>0.122 (10)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.050 (45)</t>
+          <t>0.100 (29)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.720 (16)</t>
+          <t>0.801 (7)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Reimbursement of network usage charges for Hydrogen and Power-to-X P+D installations</t>
+          <t>Subsidy on CO2 transport and storage infrastructure</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.446 (46)</t>
+          <t>0.227 (45)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.165 (25)</t>
+          <t>0.169 (33)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.030 (20)</t>
+          <t>0.024 (16)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.136 (28)</t>
+          <t>0.170 (1)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -660,34 +660,34 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.151 (12)</t>
+          <t>0.050 (45)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.494 (44)</t>
+          <t>0.591 (37)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Investment contribution for Power-to-X installations</t>
+          <t>Project planning grants for Alpine PV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.446 (46)</t>
+          <t>0.024 (16)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.165 (25)</t>
+          <t>0.140 (20)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.030 (20)</t>
+          <t>0.000 (1)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -697,24 +697,24 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.122 (10)</t>
+          <t>0.041 (1)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.100 (29)</t>
+          <t>0.050 (45)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.484 (45)</t>
+          <t>0.720 (16)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Investment contribution on green H2</t>
+          <t>Reimbursement of network usage charges for Hydrogen and Power-to-X P+D installations</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.170 (1)</t>
+          <t>0.136 (28)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -744,34 +744,34 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.050 (45)</t>
+          <t>0.151 (12)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.480 (46)</t>
+          <t>0.494 (44)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Subsidy on purchasing light FCEV</t>
+          <t>Investment contribution for Power-to-X installations</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.130 (37)</t>
+          <t>0.446 (46)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.013 (1)</t>
+          <t>0.165 (25)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.000 (1)</t>
+          <t>0.030 (20)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -781,101 +781,227 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.204 (34)</t>
+          <t>0.122 (10)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.151 (12)</t>
+          <t>0.100 (29)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.816 (5)</t>
+          <t>0.484 (45)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Vehicle import tax exemption for FCEV</t>
+          <t>Investment contribution on green H2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.133 (38)</t>
+          <t>0.446 (46)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.016 (2)</t>
+          <t>0.165 (25)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.000 (1)</t>
+          <t>0.030 (20)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.136 (28)</t>
+          <t>0.170 (1)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.204 (34)</t>
+          <t>0.041 (1)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.201 (1)</t>
+          <t>0.050 (45)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.822 (4)</t>
+          <t>0.480 (46)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Subsidy on purchasing light FCEV</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.130 (37)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.013 (1)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.000 (1)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.170 (1)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.204 (34)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.151 (12)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.816 (5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Vehicle import tax exemption for FCEV</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.133 (38)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.016 (2)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.000 (1)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.136 (28)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.204 (34)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.201 (1)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.822 (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Subsidy on H2 filling stations</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>0.133 (38)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>0.016 (2)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>0.000 (1)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>0.170 (1)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>0.041 (1)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>0.050 (45)</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>0.778 (9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Subsidy on light EV charging infrastructure in residential or office facilities</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.074 (25)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.102 (15)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.504 (47)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.170 (1)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.204 (34)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.151 (12)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.449 (47)</t>
         </is>
       </c>
     </row>
@@ -890,7 +1016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -962,7 +1088,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Carbon removal for fossil electricity generation plants</t>
+          <t>Minimum tariffs for photovoltaic systems &lt;= 150 Kw</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -979,19 +1105,19 @@
         <v>0.183</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0124</v>
+        <v>0.0332</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P+D subsidy on DACCS</t>
+          <t>Carbon removal for fossil electricity generation plants</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1020,7 +1146,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Project planning grants for Alpine PV</t>
+          <t>P+D subsidy on DACCS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1037,19 +1163,19 @@
         <v>0.183</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0243</v>
+        <v>0.0124</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Reimbursement of network usage charges for Hydrogen and Power-to-X P+D installations</t>
+          <t>Subsidy on CO2 transport and storage infrastructure</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1066,19 +1192,19 @@
         <v>0.183</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4461</v>
+        <v>0.2266</v>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Investment contribution for Power-to-X installations</t>
+          <t>Project planning grants for Alpine PV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1095,19 +1221,19 @@
         <v>0.183</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4461</v>
+        <v>0.0243</v>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Investment contribution on green H2</t>
+          <t>Reimbursement of network usage charges for Hydrogen and Power-to-X P+D installations</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1136,7 +1262,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Subsidy on purchasing light FCEV</t>
+          <t>Investment contribution for Power-to-X installations</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,19 +1279,19 @@
         <v>0.183</v>
       </c>
       <c r="E9" t="n">
-        <v>0.13</v>
+        <v>0.4461</v>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Vehicle import tax exemption for FCEV</t>
+          <t>Investment contribution on green H2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,19 +1308,19 @@
         <v>0.183</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1331</v>
+        <v>0.4461</v>
       </c>
       <c r="F10" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Subsidy on H2 filling stations</t>
+          <t>Subsidy on purchasing light FCEV</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1211,24 +1337,24 @@
         <v>0.183</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1331</v>
+        <v>0.13</v>
       </c>
       <c r="F11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Subsidy on heat pumps</t>
+          <t>Vehicle import tax exemption for FCEV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>c3 Social_acceptance_tech</t>
+          <t>c1 Cost_carbon_abatement</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1237,27 +1363,27 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.308</v>
+        <v>0.183</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1479</v>
+        <v>0.1331</v>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Carbon removal for fossil electricity generation plants</t>
+          <t>Subsidy on H2 filling stations</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>c3 Social_acceptance_tech</t>
+          <t>c1 Cost_carbon_abatement</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1266,13 +1392,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.308</v>
+        <v>0.183</v>
       </c>
       <c r="E13" t="n">
-        <v>0.094</v>
+        <v>0.1331</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
@@ -1281,12 +1407,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P+D subsidy on DACCS</t>
+          <t>Subsidy on light EV charging infrastructure in residential or office facilities</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>c3 Social_acceptance_tech</t>
+          <t>c1 Cost_carbon_abatement</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1295,13 +1421,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.308</v>
+        <v>0.183</v>
       </c>
       <c r="E14" t="n">
-        <v>0.094</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
@@ -1310,7 +1436,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Project planning grants for Alpine PV</t>
+          <t>Subsidy on heat pumps</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1327,10 +1453,10 @@
         <v>0.308</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1404</v>
+        <v>0.1479</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -1339,7 +1465,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Reimbursement of network usage charges for Hydrogen and Power-to-X P+D installations</t>
+          <t>Minimum tariffs for photovoltaic systems &lt;= 150 Kw</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1356,19 +1482,19 @@
         <v>0.308</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1655</v>
+        <v>0.2257</v>
       </c>
       <c r="F16" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Investment contribution for Power-to-X installations</t>
+          <t>Carbon removal for fossil electricity generation plants</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1385,19 +1511,19 @@
         <v>0.308</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1655</v>
+        <v>0.094</v>
       </c>
       <c r="F17" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Investment contribution on green H2</t>
+          <t>P+D subsidy on DACCS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1414,19 +1540,19 @@
         <v>0.308</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1655</v>
+        <v>0.094</v>
       </c>
       <c r="F18" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Subsidy on purchasing light FCEV</t>
+          <t>Subsidy on CO2 transport and storage infrastructure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1443,10 +1569,10 @@
         <v>0.308</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0125</v>
+        <v>0.1689</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -1455,7 +1581,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Vehicle import tax exemption for FCEV</t>
+          <t>Project planning grants for Alpine PV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1472,19 +1598,19 @@
         <v>0.308</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0163</v>
+        <v>0.1404</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Subsidy on H2 filling stations</t>
+          <t>Reimbursement of network usage charges for Hydrogen and Power-to-X P+D installations</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1501,24 +1627,24 @@
         <v>0.308</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0163</v>
+        <v>0.1655</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Subsidy on heat pumps</t>
+          <t>Investment contribution for Power-to-X installations</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>c4 Deployment_difficulty</t>
+          <t>c3 Social_acceptance_tech</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1527,27 +1653,27 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.183</v>
+        <v>0.308</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1789</v>
+        <v>0.1655</v>
       </c>
       <c r="F22" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Carbon removal for fossil electricity generation plants</t>
+          <t>Investment contribution on green H2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>c4 Deployment_difficulty</t>
+          <t>c3 Social_acceptance_tech</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1556,27 +1682,27 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.183</v>
+        <v>0.308</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.1655</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P+D subsidy on DACCS</t>
+          <t>Subsidy on purchasing light FCEV</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>c4 Deployment_difficulty</t>
+          <t>c3 Social_acceptance_tech</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1585,27 +1711,27 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.183</v>
+        <v>0.308</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Project planning grants for Alpine PV</t>
+          <t>Vehicle import tax exemption for FCEV</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>c4 Deployment_difficulty</t>
+          <t>c3 Social_acceptance_tech</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1614,27 +1740,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.183</v>
+        <v>0.308</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>0.0163</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Reimbursement of network usage charges for Hydrogen and Power-to-X P+D installations</t>
+          <t>Subsidy on H2 filling stations</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>c4 Deployment_difficulty</t>
+          <t>c3 Social_acceptance_tech</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1643,27 +1769,27 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.183</v>
+        <v>0.308</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0299</v>
+        <v>0.0163</v>
       </c>
       <c r="F26" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Investment contribution for Power-to-X installations</t>
+          <t>Subsidy on light EV charging infrastructure in residential or office facilities</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>c4 Deployment_difficulty</t>
+          <t>c3 Social_acceptance_tech</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1672,22 +1798,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.183</v>
+        <v>0.308</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0299</v>
+        <v>0.1016</v>
       </c>
       <c r="F27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Investment contribution on green H2</t>
+          <t>Subsidy on heat pumps</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1704,19 +1830,19 @@
         <v>0.183</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0299</v>
+        <v>0.1789</v>
       </c>
       <c r="F28" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Subsidy on purchasing light FCEV</t>
+          <t>Minimum tariffs for photovoltaic systems &lt;= 150 Kw</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1733,19 +1859,19 @@
         <v>0.183</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>0.2204</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="G29" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Vehicle import tax exemption for FCEV</t>
+          <t>Carbon removal for fossil electricity generation plants</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1774,7 +1900,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Subsidy on H2 filling stations</t>
+          <t>P+D subsidy on DACCS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1803,268 +1929,268 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Subsidy on heat pumps</t>
+          <t>Subsidy on CO2 transport and storage infrastructure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>c5 Acceptance_policy_instrument</t>
+          <t>c4 Deployment_difficulty</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.05</v>
+        <v>0.183</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1699</v>
+        <v>0.024</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G32" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Carbon removal for fossil electricity generation plants</t>
+          <t>Project planning grants for Alpine PV</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>c5 Acceptance_policy_instrument</t>
+          <t>c4 Deployment_difficulty</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.05</v>
+        <v>0.183</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1019</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>P+D subsidy on DACCS</t>
+          <t>Reimbursement of network usage charges for Hydrogen and Power-to-X P+D installations</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>c5 Acceptance_policy_instrument</t>
+          <t>c4 Deployment_difficulty</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.05</v>
+        <v>0.183</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1699</v>
+        <v>0.0299</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G34" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Project planning grants for Alpine PV</t>
+          <t>Investment contribution for Power-to-X installations</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>c5 Acceptance_policy_instrument</t>
+          <t>c4 Deployment_difficulty</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.05</v>
+        <v>0.183</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1699</v>
+        <v>0.0299</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G35" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Reimbursement of network usage charges for Hydrogen and Power-to-X P+D installations</t>
+          <t>Investment contribution on green H2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>c5 Acceptance_policy_instrument</t>
+          <t>c4 Deployment_difficulty</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.05</v>
+        <v>0.183</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1359</v>
+        <v>0.0299</v>
       </c>
       <c r="F36" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Investment contribution for Power-to-X installations</t>
+          <t>Subsidy on purchasing light FCEV</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>c5 Acceptance_policy_instrument</t>
+          <t>c4 Deployment_difficulty</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.05</v>
+        <v>0.183</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1699</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Investment contribution on green H2</t>
+          <t>Vehicle import tax exemption for FCEV</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>c5 Acceptance_policy_instrument</t>
+          <t>c4 Deployment_difficulty</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.05</v>
+        <v>0.183</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1699</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Subsidy on purchasing light FCEV</t>
+          <t>Subsidy on H2 filling stations</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>c5 Acceptance_policy_instrument</t>
+          <t>c4 Deployment_difficulty</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.05</v>
+        <v>0.183</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1699</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Vehicle import tax exemption for FCEV</t>
+          <t>Subsidy on light EV charging infrastructure in residential or office facilities</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>c5 Acceptance_policy_instrument</t>
+          <t>c4 Deployment_difficulty</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.05</v>
+        <v>0.183</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1359</v>
+        <v>0.504</v>
       </c>
       <c r="F40" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G40" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Subsidy on H2 filling stations</t>
+          <t>Subsidy on heat pumps</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2093,30 +2219,30 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Subsidy on heat pumps</t>
+          <t>Minimum tariffs for photovoltaic systems &lt;= 150 Kw</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>c6 Administrative_burden</t>
+          <t>c5 Acceptance_policy_instrument</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.092</v>
+        <v>0.05</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2041</v>
+        <v>0.1359</v>
       </c>
       <c r="F42" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G42" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
@@ -2127,25 +2253,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>c6 Administrative_burden</t>
+          <t>c5 Acceptance_policy_instrument</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.092</v>
+        <v>0.05</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0408</v>
+        <v>0.1019</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="G43" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
@@ -2156,239 +2282,239 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>c6 Administrative_burden</t>
+          <t>c5 Acceptance_policy_instrument</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.092</v>
+        <v>0.05</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1225</v>
+        <v>0.1699</v>
       </c>
       <c r="F44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Project planning grants for Alpine PV</t>
+          <t>Subsidy on CO2 transport and storage infrastructure</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>c6 Administrative_burden</t>
+          <t>c5 Acceptance_policy_instrument</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.092</v>
+        <v>0.05</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0408</v>
+        <v>0.1699</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Reimbursement of network usage charges for Hydrogen and Power-to-X P+D installations</t>
+          <t>Project planning grants for Alpine PV</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>c6 Administrative_burden</t>
+          <t>c5 Acceptance_policy_instrument</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.092</v>
+        <v>0.05</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0408</v>
+        <v>0.1699</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Investment contribution for Power-to-X installations</t>
+          <t>Reimbursement of network usage charges for Hydrogen and Power-to-X P+D installations</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>c6 Administrative_burden</t>
+          <t>c5 Acceptance_policy_instrument</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.092</v>
+        <v>0.05</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1225</v>
+        <v>0.1359</v>
       </c>
       <c r="F47" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="G47" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Investment contribution on green H2</t>
+          <t>Investment contribution for Power-to-X installations</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>c6 Administrative_burden</t>
+          <t>c5 Acceptance_policy_instrument</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.092</v>
+        <v>0.05</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0408</v>
+        <v>0.1699</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Subsidy on purchasing light FCEV</t>
+          <t>Investment contribution on green H2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>c6 Administrative_burden</t>
+          <t>c5 Acceptance_policy_instrument</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.092</v>
+        <v>0.05</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2041</v>
+        <v>0.1699</v>
       </c>
       <c r="F49" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Vehicle import tax exemption for FCEV</t>
+          <t>Subsidy on purchasing light FCEV</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>c6 Administrative_burden</t>
+          <t>c5 Acceptance_policy_instrument</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.092</v>
+        <v>0.05</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2041</v>
+        <v>0.1699</v>
       </c>
       <c r="F50" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Subsidy on H2 filling stations</t>
+          <t>Vehicle import tax exemption for FCEV</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>c6 Administrative_burden</t>
+          <t>c5 Acceptance_policy_instrument</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.092</v>
+        <v>0.05</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0408</v>
+        <v>0.1359</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="G51" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Subsidy on heat pumps</t>
+          <t>Subsidy on H2 filling stations</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>c7 Perceived_equity</t>
+          <t>c5 Acceptance_policy_instrument</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2397,27 +2523,27 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.183</v>
+        <v>0.05</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1506</v>
+        <v>0.1699</v>
       </c>
       <c r="F52" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Carbon removal for fossil electricity generation plants</t>
+          <t>Subsidy on light EV charging infrastructure in residential or office facilities</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>c7 Perceived_equity</t>
+          <t>c5 Acceptance_policy_instrument</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2426,248 +2552,770 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.183</v>
+        <v>0.05</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2008</v>
+        <v>0.1699</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>P+D subsidy on DACCS</t>
+          <t>Subsidy on heat pumps</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>c7 Perceived_equity</t>
+          <t>c6 Administrative_burden</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.183</v>
+        <v>0.092</v>
       </c>
       <c r="E54" t="n">
-        <v>0.1004</v>
+        <v>0.2041</v>
       </c>
       <c r="F54" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G54" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Project planning grants for Alpine PV</t>
+          <t>Minimum tariffs for photovoltaic systems &lt;= 150 Kw</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>c7 Perceived_equity</t>
+          <t>c6 Administrative_burden</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.183</v>
+        <v>0.092</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0502</v>
+        <v>0.2041</v>
       </c>
       <c r="F55" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="G55" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Reimbursement of network usage charges for Hydrogen and Power-to-X P+D installations</t>
+          <t>Carbon removal for fossil electricity generation plants</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>c7 Perceived_equity</t>
+          <t>c6 Administrative_burden</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.183</v>
+        <v>0.092</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1506</v>
+        <v>0.0408</v>
       </c>
       <c r="F56" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Investment contribution for Power-to-X installations</t>
+          <t>P+D subsidy on DACCS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>c7 Perceived_equity</t>
+          <t>c6 Administrative_burden</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.183</v>
+        <v>0.092</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1004</v>
+        <v>0.1225</v>
       </c>
       <c r="F57" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G57" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Investment contribution on green H2</t>
+          <t>Subsidy on CO2 transport and storage infrastructure</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>c7 Perceived_equity</t>
+          <t>c6 Administrative_burden</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.183</v>
+        <v>0.092</v>
       </c>
       <c r="E58" t="n">
-        <v>0.0502</v>
+        <v>0.0408</v>
       </c>
       <c r="F58" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Subsidy on purchasing light FCEV</t>
+          <t>Project planning grants for Alpine PV</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>c7 Perceived_equity</t>
+          <t>c6 Administrative_burden</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.183</v>
+        <v>0.092</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1506</v>
+        <v>0.0408</v>
       </c>
       <c r="F59" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Vehicle import tax exemption for FCEV</t>
+          <t>Reimbursement of network usage charges for Hydrogen and Power-to-X P+D installations</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>c7 Perceived_equity</t>
+          <t>c6 Administrative_burden</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.183</v>
+        <v>0.092</v>
       </c>
       <c r="E60" t="n">
-        <v>0.2008</v>
+        <v>0.0408</v>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>Investment contribution for Power-to-X installations</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>c6 Administrative_burden</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="F61" t="n">
+        <v>10</v>
+      </c>
+      <c r="G61" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Investment contribution on green H2</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>c6 Administrative_burden</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.0408</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Subsidy on purchasing light FCEV</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>c6 Administrative_burden</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.2041</v>
+      </c>
+      <c r="F63" t="n">
+        <v>34</v>
+      </c>
+      <c r="G63" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Vehicle import tax exemption for FCEV</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>c6 Administrative_burden</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.2041</v>
+      </c>
+      <c r="F64" t="n">
+        <v>34</v>
+      </c>
+      <c r="G64" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>Subsidy on H2 filling stations</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>c6 Administrative_burden</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.0408</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Subsidy on light EV charging infrastructure in residential or office facilities</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>c6 Administrative_burden</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.2041</v>
+      </c>
+      <c r="F66" t="n">
+        <v>34</v>
+      </c>
+      <c r="G66" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Subsidy on heat pumps</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
         <is>
           <t>c7 Perceived_equity</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="D61" t="n">
-        <v>0.183</v>
-      </c>
-      <c r="E61" t="n">
+      <c r="D67" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="F67" t="n">
+        <v>12</v>
+      </c>
+      <c r="G67" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Minimum tariffs for photovoltaic systems &lt;= 150 Kw</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>c7 Perceived_equity</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="F68" t="n">
+        <v>12</v>
+      </c>
+      <c r="G68" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Carbon removal for fossil electricity generation plants</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>c7 Perceived_equity</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.2008</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>P+D subsidy on DACCS</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>c7 Perceived_equity</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.1004</v>
+      </c>
+      <c r="F70" t="n">
+        <v>29</v>
+      </c>
+      <c r="G70" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Subsidy on CO2 transport and storage infrastructure</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>c7 Perceived_equity</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="E71" t="n">
         <v>0.0502</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F71" t="n">
         <v>45</v>
       </c>
-      <c r="G61" t="n">
+      <c r="G71" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Project planning grants for Alpine PV</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>c7 Perceived_equity</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="F72" t="n">
+        <v>45</v>
+      </c>
+      <c r="G72" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Reimbursement of network usage charges for Hydrogen and Power-to-X P+D installations</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>c7 Perceived_equity</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="F73" t="n">
+        <v>12</v>
+      </c>
+      <c r="G73" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Investment contribution for Power-to-X installations</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>c7 Perceived_equity</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.1004</v>
+      </c>
+      <c r="F74" t="n">
+        <v>29</v>
+      </c>
+      <c r="G74" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Investment contribution on green H2</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>c7 Perceived_equity</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="F75" t="n">
+        <v>45</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Subsidy on purchasing light FCEV</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>c7 Perceived_equity</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="F76" t="n">
+        <v>12</v>
+      </c>
+      <c r="G76" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Vehicle import tax exemption for FCEV</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>c7 Perceived_equity</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.2008</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Subsidy on H2 filling stations</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>c7 Perceived_equity</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="F78" t="n">
+        <v>45</v>
+      </c>
+      <c r="G78" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Subsidy on light EV charging infrastructure in residential or office facilities</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>c7 Perceived_equity</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="F79" t="n">
+        <v>12</v>
+      </c>
+      <c r="G79" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
